--- a/migration/dam_supp.xlsx
+++ b/migration/dam_supp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\swart053\Documents\DAM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A048F943-5929-41C8-ACFA-AF2B01BAB5E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6381C2D7-B7AC-4FF5-90D1-1C8B83E0187C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1116" yWindow="1116" windowWidth="17280" windowHeight="9960" xr2:uid="{3AD48394-8BBA-4A51-8D82-4739451A936B}"/>
+    <workbookView xWindow="2256" yWindow="3636" windowWidth="17280" windowHeight="9960" xr2:uid="{3AD48394-8BBA-4A51-8D82-4739451A936B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="132">
   <si>
     <t>1d975909-26f7-f2d2-425f-3c61951d3f33</t>
   </si>
@@ -366,16 +366,91 @@
   </si>
   <si>
     <t>D10026000230</t>
+  </si>
+  <si>
+    <t>d35793bf-12dc-0e1b-e053-b784100abd1f</t>
+  </si>
+  <si>
+    <t>D10148022468.jpg</t>
+  </si>
+  <si>
+    <t>D10148022468</t>
+  </si>
+  <si>
+    <t>D10148022469.jpg</t>
+  </si>
+  <si>
+    <t>D10148022469</t>
+  </si>
+  <si>
+    <t>D10148022470.jpg</t>
+  </si>
+  <si>
+    <t>D10148022470</t>
+  </si>
+  <si>
+    <t>D10148022471.jpg</t>
+  </si>
+  <si>
+    <t>D10148022471</t>
+  </si>
+  <si>
+    <t>17035807-cd46-9e4c-0828-78ec4cf67818</t>
+  </si>
+  <si>
+    <t>D10222001278.JPG</t>
+  </si>
+  <si>
+    <t>D10222001278</t>
+  </si>
+  <si>
+    <t>deb77523-c41a-3e39-5754-e5945f8e5e23</t>
+  </si>
+  <si>
+    <t>D10222001279.JPG</t>
+  </si>
+  <si>
+    <t>D10222001279</t>
+  </si>
+  <si>
+    <t>D10222001280.JPG</t>
+  </si>
+  <si>
+    <t>D10222001280</t>
+  </si>
+  <si>
+    <t>D10222001281.JPG</t>
+  </si>
+  <si>
+    <t>D10222001281</t>
+  </si>
+  <si>
+    <t>3c40e7b1-3c88-ec05-ca4c-b5e59c7dbf19</t>
+  </si>
+  <si>
+    <t>D10134003935.jpg</t>
+  </si>
+  <si>
+    <t>7225be35-3528-6632-7a12-ccaaf1fcad19</t>
+  </si>
+  <si>
+    <t>D10134003960.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -400,7 +475,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -408,6 +483,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -742,7 +818,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDB390F8-4736-4E90-9F96-1D7D0DE4C8CE}">
-  <dimension ref="A1:K56"/>
+  <dimension ref="A1:K67"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="50.109375" customWidth="1"/>
@@ -2386,7 +2462,303 @@
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
     </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A57" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B57" s="2">
+        <v>30435</v>
+      </c>
+      <c r="C57" s="2">
+        <v>23</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E57" s="2">
+        <v>8025396</v>
+      </c>
+      <c r="F57" s="2">
+        <v>8025396</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="H57" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
+      <c r="K57" s="1"/>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A58" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B58" s="2">
+        <v>30435</v>
+      </c>
+      <c r="C58" s="2">
+        <v>23</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E58" s="2">
+        <v>8025396</v>
+      </c>
+      <c r="F58" s="2">
+        <v>8025396</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H58" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I58" s="1"/>
+      <c r="J58" s="1"/>
+      <c r="K58" s="1"/>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A59" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B59" s="2">
+        <v>30435</v>
+      </c>
+      <c r="C59" s="2">
+        <v>23</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E59" s="2">
+        <v>8025396</v>
+      </c>
+      <c r="F59" s="2">
+        <v>8025396</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H59" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I59" s="1"/>
+      <c r="J59" s="1"/>
+      <c r="K59" s="1"/>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A60" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B60" s="2">
+        <v>30435</v>
+      </c>
+      <c r="C60" s="2">
+        <v>23</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E60" s="2">
+        <v>8025396</v>
+      </c>
+      <c r="F60" s="2">
+        <v>8025396</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H60" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I60" s="1"/>
+      <c r="J60" s="1"/>
+      <c r="K60" s="1"/>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A61" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B61" s="3">
+        <v>30603</v>
+      </c>
+      <c r="C61" s="3">
+        <v>1389</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E61" s="3">
+        <v>55781911</v>
+      </c>
+      <c r="F61" s="3">
+        <v>55781911</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="H61" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3"/>
+      <c r="J61" s="3"/>
+      <c r="K61" s="3"/>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A62" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B62" s="3">
+        <v>30603</v>
+      </c>
+      <c r="C62" s="3">
+        <v>1390</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E62" s="3">
+        <v>55781912</v>
+      </c>
+      <c r="F62" s="3">
+        <v>55781912</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="H62" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I62" s="3"/>
+      <c r="J62" s="3"/>
+      <c r="K62" s="3"/>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A63" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B63" s="3">
+        <v>30603</v>
+      </c>
+      <c r="C63" s="3">
+        <v>1390</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E63" s="3">
+        <v>55781912</v>
+      </c>
+      <c r="F63" s="3">
+        <v>55781912</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H63" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I63" s="3"/>
+      <c r="J63" s="3"/>
+      <c r="K63" s="3"/>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A64" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B64" s="3">
+        <v>30603</v>
+      </c>
+      <c r="C64" s="3">
+        <v>1390</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E64" s="3">
+        <v>55781912</v>
+      </c>
+      <c r="F64" s="3">
+        <v>55781912</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H64" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I64" s="3"/>
+      <c r="J64" s="3"/>
+      <c r="K64" s="3"/>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A65" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B65" s="2">
+        <v>10192</v>
+      </c>
+      <c r="C65" s="2">
+        <v>2680</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E65" s="1"/>
+      <c r="F65" s="1"/>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1"/>
+      <c r="J65" s="1"/>
+      <c r="K65" s="1"/>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A66" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B66" s="2">
+        <v>10192</v>
+      </c>
+      <c r="C66" s="2">
+        <v>2680</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="1"/>
+      <c r="K66" s="1"/>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A67" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B67" s="2">
+        <v>10192</v>
+      </c>
+      <c r="C67" s="2">
+        <v>2681</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E67" s="1"/>
+      <c r="F67" s="1"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="1"/>
+      <c r="J67" s="1"/>
+      <c r="K67" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>